--- a/artfynd/A 24459-2024 artfynd.xlsx
+++ b/artfynd/A 24459-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111630815</v>
       </c>
       <c r="B2" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560238</v>
+        <v>560239</v>
       </c>
       <c r="R2" t="n">
         <v>7027324</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111630821</v>
+        <v>111630816</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560368</v>
+        <v>560239</v>
       </c>
       <c r="R3" t="n">
-        <v>7027192</v>
+        <v>7027324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111630819</v>
+        <v>111726550</v>
       </c>
       <c r="B4" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långflon, Ång</t>
+          <t>Sämtjärnbäcken, Lövåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560373</v>
+        <v>560178</v>
       </c>
       <c r="R4" t="n">
-        <v>7027216</v>
+        <v>7027408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,27 +954,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111630822</v>
+        <v>111726555</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långflon, Ång</t>
+          <t>Sämtjärnbäcken, Lövåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560347</v>
+        <v>560211</v>
       </c>
       <c r="R5" t="n">
-        <v>7027195</v>
+        <v>7027448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,49 +1055,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111630817</v>
+        <v>111630819</v>
       </c>
       <c r="B6" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560250</v>
+        <v>560373</v>
       </c>
       <c r="R6" t="n">
-        <v>7027340</v>
+        <v>7027216</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111630820</v>
+        <v>111630818</v>
       </c>
       <c r="B7" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560376</v>
+        <v>560346</v>
       </c>
       <c r="R7" t="n">
-        <v>7027175</v>
+        <v>7027413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1265,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111630816</v>
+        <v>111630822</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560238</v>
+        <v>560347</v>
       </c>
       <c r="R8" t="n">
-        <v>7027324</v>
+        <v>7027195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,50 +1362,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111630818</v>
+        <v>111726562</v>
       </c>
       <c r="B9" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långflon, Ång</t>
+          <t>Sämtjärnbäcken, Lövåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560346</v>
+        <v>560126</v>
       </c>
       <c r="R9" t="n">
-        <v>7027413</v>
+        <v>7027401</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,15 +1447,213 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111630821</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>560368</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7027192</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Rasmus Viding</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Rasmus Viding</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111630817</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>560250</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7027340</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24459-2024 artfynd.xlsx
+++ b/artfynd/A 24459-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630815</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630816</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726550</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726555</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630819</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630818</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726562</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630821</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,8 +1704,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>